--- a/artfynd/A 33716-2019 artfynd.xlsx
+++ b/artfynd/A 33716-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113464169</v>
+        <v>113464170</v>
       </c>
       <c r="B2" t="n">
         <v>99570</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441390</v>
+        <v>441372</v>
       </c>
       <c r="R2" t="n">
-        <v>6507958</v>
+        <v>6507949</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113464170</v>
+        <v>113464169</v>
       </c>
       <c r="B3" t="n">
         <v>99570</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441372</v>
+        <v>441390</v>
       </c>
       <c r="R3" t="n">
-        <v>6507949</v>
+        <v>6507958</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 33716-2019 artfynd.xlsx
+++ b/artfynd/A 33716-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113464170</v>
+        <v>113464169</v>
       </c>
       <c r="B2" t="n">
-        <v>99570</v>
+        <v>99582</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441372</v>
+        <v>441390</v>
       </c>
       <c r="R2" t="n">
-        <v>6507949</v>
+        <v>6507958</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113464169</v>
+        <v>113464170</v>
       </c>
       <c r="B3" t="n">
-        <v>99570</v>
+        <v>99582</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441390</v>
+        <v>441372</v>
       </c>
       <c r="R3" t="n">
-        <v>6507958</v>
+        <v>6507949</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 33716-2019 artfynd.xlsx
+++ b/artfynd/A 33716-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113464169</v>
+        <v>113464170</v>
       </c>
       <c r="B2" t="n">
         <v>99582</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441390</v>
+        <v>441372</v>
       </c>
       <c r="R2" t="n">
-        <v>6507958</v>
+        <v>6507949</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113464170</v>
+        <v>113464169</v>
       </c>
       <c r="B3" t="n">
         <v>99582</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441372</v>
+        <v>441390</v>
       </c>
       <c r="R3" t="n">
-        <v>6507949</v>
+        <v>6507958</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 33716-2019 artfynd.xlsx
+++ b/artfynd/A 33716-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113464170</v>
+        <v>113464169</v>
       </c>
       <c r="B2" t="n">
-        <v>99582</v>
+        <v>99604</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441372</v>
+        <v>441390</v>
       </c>
       <c r="R2" t="n">
-        <v>6507949</v>
+        <v>6507958</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113464169</v>
+        <v>113464170</v>
       </c>
       <c r="B3" t="n">
-        <v>99582</v>
+        <v>99604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441390</v>
+        <v>441372</v>
       </c>
       <c r="R3" t="n">
-        <v>6507958</v>
+        <v>6507949</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 33716-2019 artfynd.xlsx
+++ b/artfynd/A 33716-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113464169</v>
+        <v>113464170</v>
       </c>
       <c r="B2" t="n">
-        <v>99604</v>
+        <v>99608</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441390</v>
+        <v>441372</v>
       </c>
       <c r="R2" t="n">
-        <v>6507958</v>
+        <v>6507949</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113464170</v>
+        <v>113464169</v>
       </c>
       <c r="B3" t="n">
-        <v>99604</v>
+        <v>99608</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441372</v>
+        <v>441390</v>
       </c>
       <c r="R3" t="n">
-        <v>6507949</v>
+        <v>6507958</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 33716-2019 artfynd.xlsx
+++ b/artfynd/A 33716-2019 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113464170</v>
+        <v>113464169</v>
       </c>
       <c r="B2" t="n">
-        <v>99608</v>
+        <v>99614</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441372</v>
+        <v>441390</v>
       </c>
       <c r="R2" t="n">
-        <v>6507949</v>
+        <v>6507958</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113464169</v>
+        <v>113464170</v>
       </c>
       <c r="B3" t="n">
-        <v>99608</v>
+        <v>99614</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441390</v>
+        <v>441372</v>
       </c>
       <c r="R3" t="n">
-        <v>6507958</v>
+        <v>6507949</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 33716-2019 artfynd.xlsx
+++ b/artfynd/A 33716-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113464169</v>
       </c>
       <c r="B2" t="n">
-        <v>99614</v>
+        <v>99621</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>113464170</v>
       </c>
       <c r="B3" t="n">
-        <v>99614</v>
+        <v>99621</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 33716-2019 artfynd.xlsx
+++ b/artfynd/A 33716-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113464169</v>
       </c>
       <c r="B2" t="n">
-        <v>99621</v>
+        <v>99626</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>113464170</v>
       </c>
       <c r="B3" t="n">
-        <v>99621</v>
+        <v>99626</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 33716-2019 artfynd.xlsx
+++ b/artfynd/A 33716-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113464169</v>
       </c>
       <c r="B2" t="n">
-        <v>99626</v>
+        <v>99655</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>113464170</v>
       </c>
       <c r="B3" t="n">
-        <v>99626</v>
+        <v>99655</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 33716-2019 artfynd.xlsx
+++ b/artfynd/A 33716-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113464169</v>
       </c>
       <c r="B2" t="n">
-        <v>99655</v>
+        <v>99659</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>113464170</v>
       </c>
       <c r="B3" t="n">
-        <v>99655</v>
+        <v>99659</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 33716-2019 artfynd.xlsx
+++ b/artfynd/A 33716-2019 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113464169</v>
+        <v>113464170</v>
       </c>
       <c r="B2" t="n">
         <v>99659</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>441390</v>
+        <v>441372</v>
       </c>
       <c r="R2" t="n">
-        <v>6507958</v>
+        <v>6507949</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113464170</v>
+        <v>113464169</v>
       </c>
       <c r="B3" t="n">
         <v>99659</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>441372</v>
+        <v>441390</v>
       </c>
       <c r="R3" t="n">
-        <v>6507949</v>
+        <v>6507958</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 33716-2019 artfynd.xlsx
+++ b/artfynd/A 33716-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
